--- a/output/2026-08-31_16_Italia_Emilia_Romagna_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-08-31_16_Italia_Emilia_Romagna_Impiantistica_aspirazione_industriale.xlsx
@@ -1038,7 +1038,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Il sito principale cemgroupsrl.com verte su pompe di lubrificazione automatica; la divisione aspirazione industriale è documentata sul dominio separato aspirazione-industriale.it. Email non reperita.</t>
+          <t>Il sito principale cemgroupsrl.com verte su pompe di lubrificazione automatica; la divisione aspirazione industriale è documentata sul dominio separato aspirazione-industriale.it. Email non reperita. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
